--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ120"/>
+  <dimension ref="A1:AZ122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6126,45 +6126,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>153816</v>
+        <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>105458</v>
+        <v>106474</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>527</v>
+        <v>340</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sandnejlika</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dianthus arenarius</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 650 m NNV, Sk</t>
+          <t>Vittskövle driva. Källslund, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448128</v>
+        <v>447780</v>
       </c>
       <c r="R48" t="n">
-        <v>6191274</v>
+        <v>6191206</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6191,22 +6203,22 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>M-Kri-0431</t>
+          <t>M-Kri-0629</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>1990-05-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>1990-05-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>2D8j3926, 2D8j3927, 2D8j4026, 2D8j4027</t>
+          <t>Koordinaten justerad</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6215,23 +6227,19 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Via Skåne Floraväktarna</t>
+          <t>Charlotte Wigermo, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6241,51 +6249,60 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/153816</t>
+          <t>https://artportalen.se/Sighting/137154797</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>154457</v>
+        <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>105459</v>
+        <v>106474</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>527</v>
+        <v>340</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sandnejlika</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dianthus arenarius</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vittskövle driva. Prästlönebostället, 500 m NNO, Sk</t>
+          <t>Vittskövle driva. Källslund, 700 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448492</v>
+        <v>448282</v>
       </c>
       <c r="R49" t="n">
-        <v>6191041</v>
+        <v>6191203</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6312,17 +6329,17 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>M-Kri-0427</t>
+          <t>M-Kri-0243</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>1994-07-19</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1994-07-19</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6333,21 +6350,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
+          <t>Charlotte Wigermo, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6357,13 +6369,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/154457</t>
+          <t>https://artportalen.se/Sighting/137162114</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>154459</v>
+        <v>153816</v>
       </c>
       <c r="B50" t="n">
         <v>105458</v>
@@ -6394,14 +6406,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 650 m NV, Sk</t>
+          <t>Prästlönebostället, 650 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447738</v>
+        <v>448128</v>
       </c>
       <c r="R50" t="n">
-        <v>6191135</v>
+        <v>6191274</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6428,22 +6440,22 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>M-Kri-0429</t>
+          <t>M-Kri-0431</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>1994-07-19</t>
+          <t>1990-05-05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>1994-07-19</t>
+          <t>1990-05-05</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2D8j3822, 2D8j3823, 2D8j3922, 2D8j4022</t>
+          <t>2D8j3926, 2D8j3927, 2D8j4026, 2D8j4027</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6478,16 +6490,16 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/154459</t>
+          <t>https://artportalen.se/Sighting/153816</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>155045</v>
+        <v>154457</v>
       </c>
       <c r="B51" t="n">
-        <v>105458</v>
+        <v>105459</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6515,14 +6527,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 600 m NNV, Sk</t>
+          <t>Vittskövle driva. Prästlönebostället, 500 m NNO, Sk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447987</v>
+        <v>448492</v>
       </c>
       <c r="R51" t="n">
-        <v>6191212</v>
+        <v>6191041</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6549,22 +6561,17 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>M-Kri-0430</t>
+          <t>M-Kri-0427</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
+          <t>1994-07-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>2D8j3924, 2D8j3925, 2D8j4025</t>
+          <t>1994-07-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6599,13 +6606,13 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/155045</t>
+          <t>https://artportalen.se/Sighting/154457</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>155046</v>
+        <v>154459</v>
       </c>
       <c r="B52" t="n">
         <v>105458</v>
@@ -6636,14 +6643,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 600 m norr, Sk</t>
+          <t>Prästlönebostället, 650 m NV, Sk</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>448310</v>
+        <v>447738</v>
       </c>
       <c r="R52" t="n">
-        <v>6191323</v>
+        <v>6191135</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6670,22 +6677,22 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>M-Kri-0432-biogeo</t>
+          <t>M-Kri-0429</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
+          <t>1994-07-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
+          <t>1994-07-19</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>2D8j3928, 2D8j4028, 2D8j4029, 2D8j4128</t>
+          <t>2D8j3822, 2D8j3823, 2D8j3922, 2D8j4022</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6710,7 +6717,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
+          <t>Via Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6720,16 +6727,16 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/155046</t>
+          <t>https://artportalen.se/Sighting/154459</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6834736</v>
+        <v>155045</v>
       </c>
       <c r="B53" t="n">
-        <v>105459</v>
+        <v>105458</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6755,26 +6762,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vittskövle driva, Sk</t>
+          <t>Prästlönebostället, 600 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448435</v>
+        <v>447987</v>
       </c>
       <c r="R53" t="n">
-        <v>6191261</v>
+        <v>6191212</v>
       </c>
       <c r="S53" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6796,14 +6796,24 @@
           <t>Vittskövle</t>
         </is>
       </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>M-Kri-0430</t>
+        </is>
+      </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
+          <t>1998-06-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2D8j3924, 2D8j3925, 2D8j4025</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6814,31 +6824,40 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars Erik Norbäck</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lars Erik Norbäck, Carl Jyker</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6834736</t>
+          <t>https://artportalen.se/Sighting/155045</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>16998938</v>
+        <v>155046</v>
       </c>
       <c r="B54" t="n">
-        <v>105459</v>
+        <v>105458</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6864,21 +6883,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vittskövle driva, Sk</t>
+          <t>Prästlönebostället, 600 m norr, Sk</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448498</v>
+        <v>448310</v>
       </c>
       <c r="R54" t="n">
-        <v>6191026</v>
+        <v>6191323</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6903,19 +6917,24 @@
           <t>Vittskövle</t>
         </is>
       </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>M-Kri-0432-biogeo</t>
+        </is>
+      </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2004-06-25</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2004-06-25</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Några blommande plantor.</t>
+          <t>2D8j3928, 2D8j4028, 2D8j4029, 2D8j4128</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6929,30 +6948,34 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Sanddyna, (inlandssanddyna).</t>
+          <t>gles tallskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16998938</t>
+          <t>https://artportalen.se/Sighting/155046</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>53941603</v>
+        <v>6834736</v>
       </c>
       <c r="B55" t="n">
         <v>105459</v>
@@ -6981,24 +7004,26 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vittskövle, Sk</t>
+          <t>Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>448052</v>
+        <v>448435</v>
       </c>
       <c r="R55" t="n">
-        <v>6191252</v>
+        <v>6191261</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7022,12 +7047,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2015-06-09</t>
+          <t>2013-06-27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2015-06-09</t>
+          <t>2013-06-27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7038,36 +7063,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Lars Erik Norbäck</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Lars Erik Norbäck, Carl Jyker</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/53941603</t>
+          <t>https://artportalen.se/Sighting/6834736</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>64198929</v>
+        <v>16998938</v>
       </c>
       <c r="B56" t="n">
-        <v>105458</v>
+        <v>105459</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,19 +7113,24 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Källslund, Sk</t>
+          <t>Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>448037</v>
+        <v>448498</v>
       </c>
       <c r="R56" t="n">
-        <v>6191156</v>
+        <v>6191026</v>
       </c>
       <c r="S56" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7129,17 +7154,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>1990-05-05</t>
+          <t>2004-06-25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>1990-05-05</t>
+          <t>2004-06-25</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Dianthus arenarius/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
+          <t>Några blommande plantor.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7153,42 +7178,33 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>SkFlora    144615</t>
+          <t>Sanddyna, (inlandssanddyna).</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64198929</t>
+          <t>https://artportalen.se/Sighting/16998938</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>64199658</v>
+        <v>53941603</v>
       </c>
       <c r="B57" t="n">
-        <v>105458</v>
+        <v>105459</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7214,19 +7230,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>500m OSO Källslund, Sk</t>
+          <t>Vittskövle, Sk</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447937</v>
+        <v>448052</v>
       </c>
       <c r="R57" t="n">
-        <v>6191155</v>
+        <v>6191252</v>
       </c>
       <c r="S57" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7250,17 +7271,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
+          <t>2015-06-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Dianthus arenarius/2D8j3925/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>2015-06-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7274,39 +7290,30 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>skogsväg i gles tallskog</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>SkFlora    428609</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Bengt Westman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Bengt Westman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64199658</t>
+          <t>https://artportalen.se/Sighting/53941603</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>64199666</v>
+        <v>64198929</v>
       </c>
       <c r="B58" t="n">
         <v>105458</v>
@@ -7337,14 +7344,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>900m O Källslund, Sk</t>
+          <t>Källslund, Sk</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>448335</v>
+        <v>448037</v>
       </c>
       <c r="R58" t="n">
-        <v>6191260</v>
+        <v>6191156</v>
       </c>
       <c r="S58" t="n">
         <v>100</v>
@@ -7371,17 +7378,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
+          <t>1990-05-05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
+          <t>1990-05-05</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Dianthus arenarius/2D8j4029/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Dianthus arenarius/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7395,12 +7402,12 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>gles tallskog, sparsamt</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>SkFlora    428613</t>
+          <t>SkFlora    144615</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7411,7 +7418,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
+          <t>Via Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7421,13 +7428,13 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64199666</t>
+          <t>https://artportalen.se/Sighting/64198929</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>64202336</v>
+        <v>64199658</v>
       </c>
       <c r="B59" t="n">
         <v>105458</v>
@@ -7458,14 +7465,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>500m OSO Källslund, Sk</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>448036</v>
+        <v>447937</v>
       </c>
       <c r="R59" t="n">
-        <v>6191256</v>
+        <v>6191155</v>
       </c>
       <c r="S59" t="n">
         <v>100</v>
@@ -7492,17 +7499,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Dianthus arenarius/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Dianthus arenarius/2D8j3925/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7516,12 +7523,12 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>gles tallskog</t>
+          <t>skogsväg i gles tallskog</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>SkFlora    753262</t>
+          <t>SkFlora    428609</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7542,13 +7549,13 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202336</t>
+          <t>https://artportalen.se/Sighting/64199658</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>64202351</v>
+        <v>64199666</v>
       </c>
       <c r="B60" t="n">
         <v>105458</v>
@@ -7579,14 +7586,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>900m O Källslund, Sk</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447936</v>
+        <v>448335</v>
       </c>
       <c r="R60" t="n">
-        <v>6191255</v>
+        <v>6191260</v>
       </c>
       <c r="S60" t="n">
         <v>100</v>
@@ -7613,17 +7620,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Dianthus arenarius/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Dianthus arenarius/2D8j4029/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7637,12 +7644,12 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>stig i tallskog</t>
+          <t>gles tallskog, sparsamt</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>SkFlora    753269</t>
+          <t>SkFlora    428613</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7663,13 +7670,13 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202351</t>
+          <t>https://artportalen.se/Sighting/64199666</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>64202382</v>
+        <v>64202336</v>
       </c>
       <c r="B61" t="n">
         <v>105458</v>
@@ -7704,10 +7711,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>448236</v>
+        <v>448036</v>
       </c>
       <c r="R61" t="n">
-        <v>6191158</v>
+        <v>6191256</v>
       </c>
       <c r="S61" t="n">
         <v>100</v>
@@ -7744,7 +7751,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Dianthus arenarius/2D8j3928/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Dianthus arenarius/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7758,12 +7765,12 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>gles tallskog</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>SkFlora    753284</t>
+          <t>SkFlora    753262</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7784,13 +7791,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202382</t>
+          <t>https://artportalen.se/Sighting/64202336</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>64202401</v>
+        <v>64202351</v>
       </c>
       <c r="B62" t="n">
         <v>105458</v>
@@ -7825,10 +7832,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>448235</v>
+        <v>447936</v>
       </c>
       <c r="R62" t="n">
-        <v>6191258</v>
+        <v>6191255</v>
       </c>
       <c r="S62" t="n">
         <v>100</v>
@@ -7865,7 +7872,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Dianthus arenarius/2D8j4028/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Dianthus arenarius/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7879,12 +7886,12 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>stig i tallskog</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>SkFlora    753294</t>
+          <t>SkFlora    753269</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7905,13 +7912,13 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202401</t>
+          <t>https://artportalen.se/Sighting/64202351</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>64202435</v>
+        <v>64202382</v>
       </c>
       <c r="B63" t="n">
         <v>105458</v>
@@ -7946,10 +7953,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447837</v>
+        <v>448236</v>
       </c>
       <c r="R63" t="n">
-        <v>6191153</v>
+        <v>6191158</v>
       </c>
       <c r="S63" t="n">
         <v>100</v>
@@ -7986,7 +7993,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Dianthus arenarius/2D8j3924/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Dianthus arenarius/2D8j3928/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8000,12 +8007,12 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>gles tallskog</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>SkFlora    753311</t>
+          <t>SkFlora    753284</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8026,16 +8033,16 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202435</t>
+          <t>https://artportalen.se/Sighting/64202382</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>64416434</v>
+        <v>64202401</v>
       </c>
       <c r="B64" t="n">
-        <v>105459</v>
+        <v>105458</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8063,17 +8070,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vittskövle, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>448259</v>
+        <v>448235</v>
       </c>
       <c r="R64" t="n">
-        <v>6191381</v>
+        <v>6191258</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8097,17 +8104,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2005-06-21</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2005-06-21</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>visad av Bengt Nilsson</t>
+          <t>Dianthus arenarius/2D8j4028/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8121,33 +8128,42 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>SkFlora    753294</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64416434</t>
+          <t>https://artportalen.se/Sighting/64202401</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>86295649</v>
+        <v>64202435</v>
       </c>
       <c r="B65" t="n">
-        <v>105459</v>
+        <v>105458</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8172,36 +8188,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källslund, Vittskövle, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>448261</v>
+        <v>447837</v>
       </c>
       <c r="R65" t="n">
-        <v>6191359</v>
+        <v>6191153</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8225,17 +8225,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Dianthus arenarius/2D8j3924/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8244,31 +8244,44 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>SkFlora    753311</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86295649</t>
+          <t>https://artportalen.se/Sighting/64202435</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>86463747</v>
+        <v>64416434</v>
       </c>
       <c r="B66" t="n">
         <v>105459</v>
@@ -8297,27 +8310,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sanddrivan, Sk</t>
+          <t>Vittskövle, Sk</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>448246</v>
+        <v>448259</v>
       </c>
       <c r="R66" t="n">
-        <v>6191372</v>
+        <v>6191381</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8341,22 +8346,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2005-06-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2005-06-21</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>visad av Bengt Nilsson</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8367,31 +8367,36 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bert Östholm</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bert Östholm</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86463747</t>
+          <t>https://artportalen.se/Sighting/64416434</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>109543229</v>
+        <v>86295649</v>
       </c>
       <c r="B67" t="n">
-        <v>105458</v>
+        <v>105459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8416,20 +8421,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Källslund, 700 m öster, Sk</t>
+          <t>Källslund, Vittskövle, Sk</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>448294</v>
+        <v>448261</v>
       </c>
       <c r="R67" t="n">
-        <v>6191369</v>
+        <v>6191359</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8453,17 +8474,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>För tidigt att räkna</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8472,55 +8493,56 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Krister Wahlström</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Sofia Lund</t>
+          <t>Krister Wahlström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109543229</t>
+          <t>https://artportalen.se/Sighting/86295649</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6834737</v>
+        <v>86463747</v>
       </c>
       <c r="B68" t="n">
-        <v>108387</v>
+        <v>105459</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>762</v>
+        <v>527</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Sandnejlika</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Dianthus arenarius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8531,19 +8553,20 @@
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vittskövle driva, Sk</t>
+          <t>Sanddrivan, Sk</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>448435</v>
+        <v>448246</v>
       </c>
       <c r="R68" t="n">
-        <v>6191261</v>
+        <v>6191372</v>
       </c>
       <c r="S68" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8567,12 +8590,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
+          <t>2020-06-24</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
+          <t>2020-06-24</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8587,65 +8620,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lars Erik Norbäck</t>
+          <t>Bert Östholm</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lars Erik Norbäck, Carl Jyker</t>
+          <t>Bert Östholm</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6834737</t>
+          <t>https://artportalen.se/Sighting/86463747</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>64202397</v>
+        <v>109543229</v>
       </c>
       <c r="B69" t="n">
-        <v>108386</v>
+        <v>105458</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>762</v>
+        <v>527</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Sandnejlika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Dianthus arenarius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>Källslund, 700 m öster, Sk</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>448235</v>
+        <v>448294</v>
       </c>
       <c r="R69" t="n">
-        <v>6191258</v>
+        <v>6191369</v>
       </c>
       <c r="S69" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8669,17 +8702,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium/2D8j4028/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>För tidigt att räkna</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8690,16 +8723,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>SkFlora    753292</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8709,23 +8732,19 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Charlotte Wigermo, Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202397</t>
+          <t>https://artportalen.se/Sighting/109543229</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>93986133</v>
+        <v>6834737</v>
       </c>
       <c r="B70" t="n">
         <v>108387</v>
@@ -8753,29 +8772,27 @@
           <t>(L.) Moench</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vittskövle driva. Prästlönebostället, 500 m NNV, Sk</t>
+          <t>Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>448060</v>
+        <v>448435</v>
       </c>
       <c r="R70" t="n">
-        <v>6191145</v>
+        <v>6191261</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8797,19 +8814,14 @@
           <t>Vittskövle</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>M-Kri-2193</t>
-        </is>
-      </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
+          <t>2013-06-27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
+          <t>2013-06-27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8824,69 +8836,65 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Lars Erik Norbäck</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Lars Erik Norbäck, Carl Jyker</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93986133</t>
+          <t>https://artportalen.se/Sighting/6834737</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>633653</v>
+        <v>64202397</v>
       </c>
       <c r="B71" t="n">
-        <v>100694</v>
+        <v>108386</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1888</v>
+        <v>762</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tofsäxing</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Koeleria glauca</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) DC.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vittskövle driva. Prästlönebostället, 500 m norr, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>448314</v>
+        <v>448235</v>
       </c>
       <c r="R71" t="n">
-        <v>6191233</v>
+        <v>6191258</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8908,24 +8916,19 @@
           <t>Vittskövle</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>M-Kri-1201</t>
-        </is>
-      </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>1990-06-18</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>1990-06-18</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>2D8j3925, 2D8j3926, 2D8j3928, 2D8j4025, 2D8j4026, 2D8j4127.</t>
+          <t>Helichrysum arenarium/2D8j4028/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8939,72 +8942,86 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>gles tallskog</t>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>SkFlora    753292</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson, Åke Svensson</t>
+          <t>Kjell-arne Olsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/633653</t>
+          <t>https://artportalen.se/Sighting/64202397</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>633958</v>
+        <v>93986133</v>
       </c>
       <c r="B72" t="n">
-        <v>100694</v>
+        <v>108387</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1888</v>
+        <v>762</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tofsäxing</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Koeleria glauca</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) DC.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vittskövle driva. Prästlönebostället, 700 m NV, Sk</t>
+          <t>Vittskövle driva. Prästlönebostället, 500 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447715</v>
+        <v>448060</v>
       </c>
       <c r="R72" t="n">
-        <v>6191139</v>
+        <v>6191145</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9031,22 +9048,17 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>M-Kri-1200</t>
+          <t>M-Kri-2193</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>1994-07-19</t>
+          <t>2021-05-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>1994-07-19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>2D8j3822, 2D8j3823, 2D8j3922.</t>
+          <t>2021-05-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9057,21 +9069,16 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>på och invid markväg i tallskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson, Åke Svensson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -9081,13 +9088,13 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/633958</t>
+          <t>https://artportalen.se/Sighting/93986133</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>634125</v>
+        <v>633653</v>
       </c>
       <c r="B73" t="n">
         <v>100694</v>
@@ -9118,14 +9125,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 400 m NNO, Sk</t>
+          <t>Vittskövle driva. Prästlönebostället, 500 m norr, Sk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>448499</v>
+        <v>448314</v>
       </c>
       <c r="R73" t="n">
-        <v>6191016</v>
+        <v>6191233</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9152,22 +9159,22 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>M-Kri-1386</t>
+          <t>M-Kri-1201</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>1994-07-19</t>
+          <t>1990-06-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>1994-07-19</t>
+          <t>1990-06-18</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>2D8j3830, 2D8j3931</t>
+          <t>2D8j3925, 2D8j3926, 2D8j3928, 2D8j4025, 2D8j4026, 2D8j4127.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9181,7 +9188,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>sanddyn</t>
+          <t>gles tallskog</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9192,7 +9199,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Åke Svensson, Kjell-arne Olsson</t>
+          <t>Kjell-arne Olsson, Åke Svensson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -9202,13 +9209,13 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/634125</t>
+          <t>https://artportalen.se/Sighting/633653</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>16999189</v>
+        <v>633958</v>
       </c>
       <c r="B74" t="n">
         <v>100694</v>
@@ -9239,14 +9246,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vittskövle driva, Sk</t>
+          <t>Vittskövle driva. Prästlönebostället, 700 m NV, Sk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>448448</v>
+        <v>447715</v>
       </c>
       <c r="R74" t="n">
-        <v>6191011</v>
+        <v>6191139</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9271,19 +9278,24 @@
           <t>Vittskövle</t>
         </is>
       </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>M-Kri-1200</t>
+        </is>
+      </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2004-06-25</t>
+          <t>1994-07-19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2004-06-25</t>
+          <t>1994-07-19</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Några plantor.</t>
+          <t>2D8j3822, 2D8j3823, 2D8j3922.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9297,33 +9309,37 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Sanddyna, (inlandssanddyna).</t>
+          <t>på och invid markväg i tallskog</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Kjell-arne Olsson, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16999189</t>
+          <t>https://artportalen.se/Sighting/633958</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>64198965</v>
+        <v>634125</v>
       </c>
       <c r="B75" t="n">
-        <v>100693</v>
+        <v>100694</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9351,17 +9367,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Källslund, Sk</t>
+          <t>Prästlönebostället, 400 m NNO, Sk</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>448037</v>
+        <v>448499</v>
       </c>
       <c r="R75" t="n">
-        <v>6191156</v>
+        <v>6191016</v>
       </c>
       <c r="S75" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9383,19 +9399,24 @@
           <t>Vittskövle</t>
         </is>
       </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>M-Kri-1386</t>
+        </is>
+      </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>1990-06-18</t>
+          <t>1994-07-19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>1990-06-18</t>
+          <t>1994-07-19</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Koeleria glauca/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
+          <t>2D8j3830, 2D8j3931</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9409,42 +9430,37 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>SkFlora    144635</t>
+          <t>sanddyn</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
+          <t>Åke Svensson, Kjell-arne Olsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>Skånes Flora (1989-2006)</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64198965</t>
+          <t>https://artportalen.se/Sighting/634125</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>64199626</v>
+        <v>16999189</v>
       </c>
       <c r="B76" t="n">
-        <v>100693</v>
+        <v>100694</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9472,17 +9488,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>600m NNV Prästlönebost., Sk</t>
+          <t>Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>448036</v>
+        <v>448448</v>
       </c>
       <c r="R76" t="n">
-        <v>6191256</v>
+        <v>6191011</v>
       </c>
       <c r="S76" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9506,17 +9522,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>1994-07-19</t>
+          <t>2004-06-25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>1994-07-19</t>
+          <t>2004-06-25</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Koeleria glauca/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Några plantor.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9530,39 +9546,30 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>vid markväg i tallskog</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>SkFlora    189540</t>
+          <t>Sanddyna, (inlandssanddyna).</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64199626</t>
+          <t>https://artportalen.se/Sighting/16999189</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>64202345</v>
+        <v>64198965</v>
       </c>
       <c r="B77" t="n">
         <v>100693</v>
@@ -9593,14 +9600,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>Källslund, Sk</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447936</v>
+        <v>448037</v>
       </c>
       <c r="R77" t="n">
-        <v>6191255</v>
+        <v>6191156</v>
       </c>
       <c r="S77" t="n">
         <v>100</v>
@@ -9627,17 +9634,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1990-06-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1990-06-18</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Koeleria glauca/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Koeleria glauca/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9651,12 +9658,12 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>stig i tallskog</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>SkFlora    753266</t>
+          <t>SkFlora    144635</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9667,7 +9674,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
+          <t>Via Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9677,13 +9684,13 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202345</t>
+          <t>https://artportalen.se/Sighting/64198965</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>64202365</v>
+        <v>64199626</v>
       </c>
       <c r="B78" t="n">
         <v>100693</v>
@@ -9714,14 +9721,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>600m NNV Prästlönebost., Sk</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447937</v>
+        <v>448036</v>
       </c>
       <c r="R78" t="n">
-        <v>6191155</v>
+        <v>6191256</v>
       </c>
       <c r="S78" t="n">
         <v>100</v>
@@ -9748,17 +9755,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1994-07-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1994-07-19</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Koeleria glauca/2D8j3925/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Koeleria glauca/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9772,12 +9779,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>vid markväg i tallskog</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>SkFlora    753275</t>
+          <t>SkFlora    189540</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9798,13 +9805,13 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202365</t>
+          <t>https://artportalen.se/Sighting/64199626</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>64202386</v>
+        <v>64202345</v>
       </c>
       <c r="B79" t="n">
         <v>100693</v>
@@ -9839,10 +9846,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>448236</v>
+        <v>447936</v>
       </c>
       <c r="R79" t="n">
-        <v>6191158</v>
+        <v>6191255</v>
       </c>
       <c r="S79" t="n">
         <v>100</v>
@@ -9879,7 +9886,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Koeleria glauca/2D8j3928/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Koeleria glauca/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9893,12 +9900,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>stig i tallskog</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>SkFlora    753286</t>
+          <t>SkFlora    753266</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9919,65 +9926,54 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202386</t>
+          <t>https://artportalen.se/Sighting/64202345</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>16496592</v>
+        <v>64202365</v>
       </c>
       <c r="B80" t="n">
-        <v>100795</v>
+        <v>100693</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1900</v>
+        <v>1888</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sandtimotej</t>
+          <t>Tofsäxing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phleum arenarium</t>
+          <t>Koeleria glauca</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+          <t>(Spreng.) DC.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vittskövle sanddriva, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>448490</v>
+        <v>447937</v>
       </c>
       <c r="R80" t="n">
-        <v>6191024</v>
+        <v>6191155</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10001,12 +9997,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2014-08-17</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2014-08-17</t>
+          <t>2003-07-01</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Koeleria glauca/2D8j3925/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10020,82 +10021,80 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkrik sand på höjdrygg</t>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>SkFlora    753275</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Örjan Fritz, Karin Hernborg</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16496592</t>
+          <t>https://artportalen.se/Sighting/64202365</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>16496597</v>
+        <v>64202386</v>
       </c>
       <c r="B81" t="n">
-        <v>100795</v>
+        <v>100693</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1900</v>
+        <v>1888</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sandtimotej</t>
+          <t>Tofsäxing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phleum arenarium</t>
+          <t>Koeleria glauca</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+          <t>(Spreng.) DC.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vittskövle sanddriva, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>448463</v>
+        <v>448236</v>
       </c>
       <c r="R81" t="n">
-        <v>6190995</v>
+        <v>6191158</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10119,17 +10118,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2014-08-17</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2014-08-17</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Minst detta antal plantor.</t>
+          <t>Koeleria glauca/2D8j3928/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10143,68 +10142,88 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkrik sand på höjdrygg</t>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>SkFlora    753286</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Örjan Fritz, Karin Hernborg</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16496597</t>
+          <t>https://artportalen.se/Sighting/64202386</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121216613</v>
+        <v>16496592</v>
       </c>
       <c r="B82" t="n">
-        <v>91334</v>
+        <v>100795</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2009</v>
+        <v>1900</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Sandtimotej</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Phleum arenarium</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Källslund, 750 m öster, Sk</t>
+          <t>Vittskövle sanddriva, Sk</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>448306</v>
+        <v>448490</v>
       </c>
       <c r="R82" t="n">
-        <v>6191346</v>
+        <v>6191024</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10231,12 +10250,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2014-08-17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2014-08-17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10250,68 +10269,79 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Gles tallskog</t>
+          <t>Kalkrik sand på höjdrygg</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Örjan Fritz, Karin Hernborg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121216613</t>
+          <t>https://artportalen.se/Sighting/16496592</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121216618</v>
+        <v>16496597</v>
       </c>
       <c r="B83" t="n">
-        <v>91334</v>
+        <v>100795</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2009</v>
+        <v>1900</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Sandtimotej</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Phleum arenarium</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källslund, 700 m OSO, Sk</t>
+          <t>Vittskövle sanddriva, Sk</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>448294</v>
+        <v>448463</v>
       </c>
       <c r="R83" t="n">
-        <v>6191270</v>
+        <v>6190995</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10338,12 +10368,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2014-08-17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2014-08-17</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Minst detta antal plantor.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10357,30 +10392,30 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Gles tallskog</t>
+          <t>Kalkrik sand på höjdrygg</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Örjan Fritz, Karin Hernborg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121216618</t>
+          <t>https://artportalen.se/Sighting/16496597</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121216619</v>
+        <v>121216613</v>
       </c>
       <c r="B84" t="n">
         <v>91334</v>
@@ -10411,14 +10446,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Källslund, 700 m OSO, Sk</t>
+          <t>Källslund, 750 m öster, Sk</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>448297</v>
+        <v>448306</v>
       </c>
       <c r="R84" t="n">
-        <v>6191262</v>
+        <v>6191346</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10481,13 +10516,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121216619</t>
+          <t>https://artportalen.se/Sighting/121216613</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121360247</v>
+        <v>121216618</v>
       </c>
       <c r="B85" t="n">
         <v>91334</v>
@@ -10518,14 +10553,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Källslund, 600 m OSO, Sk</t>
+          <t>Källslund, 700 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>448137</v>
+        <v>448294</v>
       </c>
       <c r="R85" t="n">
-        <v>6191194</v>
+        <v>6191270</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10588,13 +10623,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121360247</t>
+          <t>https://artportalen.se/Sighting/121216618</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122450699</v>
+        <v>121216619</v>
       </c>
       <c r="B86" t="n">
         <v>91334</v>
@@ -10625,17 +10660,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Källslund, 750 m öster, Sk</t>
+          <t>Källslund, 700 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>448305</v>
+        <v>448297</v>
       </c>
       <c r="R86" t="n">
-        <v>6191369</v>
+        <v>6191262</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10659,12 +10694,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10675,6 +10710,11 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Gles tallskog</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10684,23 +10724,19 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Tony Svensson, Crister Albinsson, Carl-Axel Andersson, Patrik Celander, Ulf Gärdenfors</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Puggehatten, exkursion</t>
-        </is>
-      </c>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122450699</t>
+          <t>https://artportalen.se/Sighting/121216619</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123704396</v>
+        <v>121360247</v>
       </c>
       <c r="B87" t="n">
         <v>91334</v>
@@ -10729,22 +10765,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Källslund, Sk</t>
+          <t>Källslund, 600 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>448139</v>
+        <v>448137</v>
       </c>
       <c r="R87" t="n">
-        <v>6191177</v>
+        <v>6191194</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10768,17 +10801,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Två gamla fruktkroppar</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10787,34 +10815,38 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Gles tallskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123704396</t>
+          <t>https://artportalen.se/Sighting/121360247</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>89724948</v>
+        <v>122450699</v>
       </c>
       <c r="B88" t="n">
-        <v>91329</v>
+        <v>91334</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10822,48 +10854,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4191</v>
+        <v>2009</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Källslund, 500 m OSO, Sk</t>
+          <t>Källslund, 750 m öster, Sk</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447876</v>
+        <v>448305</v>
       </c>
       <c r="R88" t="n">
-        <v>6191194</v>
+        <v>6191369</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10887,12 +10908,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10901,7 +10922,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10913,60 +10933,67 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Charlotte Wigermo, Tony Svensson, Crister Albinsson, Carl-Axel Andersson, Patrik Celander, Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89724948</t>
+          <t>https://artportalen.se/Sighting/122450699</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122450695</v>
+        <v>123704396</v>
       </c>
       <c r="B89" t="n">
-        <v>91930</v>
+        <v>91334</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>2009</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Källslund, 750 m OSO, Sk</t>
+          <t>Källslund, Sk</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>448292</v>
+        <v>448139</v>
       </c>
       <c r="R89" t="n">
-        <v>6191182</v>
+        <v>6191177</v>
       </c>
       <c r="S89" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10990,12 +11017,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Två gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11004,75 +11036,83 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Tony Svensson, Crister Albinsson, Carl-Axel Andersson, Patrik Celander, Ulf Gärdenfors</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Puggehatten, exkursion</t>
-        </is>
-      </c>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122450695</t>
+          <t>https://artportalen.se/Sighting/123704396</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117691153</v>
+        <v>89724948</v>
       </c>
       <c r="B90" t="n">
-        <v>58018</v>
+        <v>91329</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100094</v>
+        <v>4191</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sommargylling</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Oriolus oriolus</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Källslund, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447987</v>
+        <v>447876</v>
       </c>
       <c r="R90" t="n">
-        <v>6191212</v>
+        <v>6191194</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11096,12 +11136,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11110,6 +11150,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11127,54 +11168,54 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117691153</t>
+          <t>https://artportalen.se/Sighting/89724948</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>80656754</v>
+        <v>122450695</v>
       </c>
       <c r="B91" t="n">
-        <v>45044</v>
+        <v>91930</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>102018</v>
+        <v>5442</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 450 m NNV, Sk</t>
+          <t>Källslund, 750 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447708</v>
+        <v>448292</v>
       </c>
       <c r="R91" t="n">
-        <v>6191230</v>
+        <v>6191182</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11198,12 +11239,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11223,57 +11264,61 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Charlotte Wigermo, Tony Svensson, Crister Albinsson, Carl-Axel Andersson, Patrik Celander, Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80656754</t>
+          <t>https://artportalen.se/Sighting/122450695</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>85929311</v>
+        <v>117691153</v>
       </c>
       <c r="B92" t="n">
-        <v>58238</v>
+        <v>58018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103012</v>
+        <v>100094</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sommargylling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Oriolus oriolus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 400 m NNO, Sk</t>
+          <t>Källslund, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>448510</v>
+        <v>447987</v>
       </c>
       <c r="R92" t="n">
-        <v>6191039</v>
+        <v>6191212</v>
       </c>
       <c r="S92" t="n">
         <v>50</v>
@@ -11300,12 +11345,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11331,62 +11376,54 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85929311</t>
+          <t>https://artportalen.se/Sighting/117691153</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122090041</v>
+        <v>80656754</v>
       </c>
       <c r="B93" t="n">
-        <v>56689</v>
+        <v>45044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>206046</v>
+        <v>102018</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vittskövle driva, Sk</t>
+          <t>Prästlönebostället, 450 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>448335</v>
+        <v>447708</v>
       </c>
       <c r="R93" t="n">
-        <v>6191260</v>
+        <v>6191230</v>
       </c>
       <c r="S93" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11410,22 +11447,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11440,65 +11467,65 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Carl-Axel Andersson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122090041</t>
+          <t>https://artportalen.se/Sighting/80656754</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>64198940</v>
+        <v>85929311</v>
       </c>
       <c r="B94" t="n">
-        <v>99096</v>
+        <v>58238</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219798</v>
+        <v>103012</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Källslund, Sk</t>
+          <t>Prästlönebostället, 400 m NNO, Sk</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>448037</v>
+        <v>448510</v>
       </c>
       <c r="R94" t="n">
-        <v>6191156</v>
+        <v>6191039</v>
       </c>
       <c r="S94" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11522,17 +11549,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>1990-06-02</t>
+          <t>2020-05-31</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>1990-06-02</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Epipactis helleborine/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
+          <t>2020-05-31</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11543,16 +11565,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>SkFlora    144621</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11562,26 +11574,22 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64198940</t>
+          <t>https://artportalen.se/Sighting/85929311</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>64200341</v>
+        <v>122090041</v>
       </c>
       <c r="B95" t="n">
-        <v>108115</v>
+        <v>56689</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11589,37 +11597,45 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220079</v>
+        <v>206046</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>1,2 km V Ängagården, Sk</t>
+          <t>Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>448036</v>
+        <v>448335</v>
       </c>
       <c r="R95" t="n">
-        <v>6191256</v>
+        <v>6191260</v>
       </c>
       <c r="S95" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11643,17 +11659,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>2025-01-11</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Cirsium acaule/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>2025-01-11</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11664,67 +11685,53 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>skogsväg, tallskog</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>SkFlora    511048</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Carl-Axel Andersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Carl-Axel Andersson, Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64200341</t>
+          <t>https://artportalen.se/Sighting/122090041</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>64198935</v>
+        <v>64198940</v>
       </c>
       <c r="B96" t="n">
-        <v>104639</v>
+        <v>99096</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220164</v>
+        <v>219798</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11774,7 +11781,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
+          <t>Epipactis helleborine/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11793,7 +11800,7 @@
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>SkFlora    144618</t>
+          <t>SkFlora    144621</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11814,54 +11821,54 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64198935</t>
+          <t>https://artportalen.se/Sighting/64198940</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>81370389</v>
+        <v>64200341</v>
       </c>
       <c r="B97" t="n">
-        <v>106156</v>
+        <v>108115</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221141</v>
+        <v>220079</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>SO Källslund, Sk</t>
+          <t>1,2 km V Ängagården, Sk</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447837</v>
+        <v>448036</v>
       </c>
       <c r="R97" t="n">
-        <v>6191153</v>
+        <v>6191256</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11885,12 +11892,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Cirsium acaule/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11904,7 +11916,12 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Gles tallskog</t>
+          <t>skogsväg, tallskog</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>SkFlora    511048</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11920,56 +11937,56 @@
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>Skånes Flora Millora 2008-2015</t>
+          <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81370389</t>
+          <t>https://artportalen.se/Sighting/64200341</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>64202353</v>
+        <v>64198935</v>
       </c>
       <c r="B98" t="n">
-        <v>106243</v>
+        <v>104639</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221144</v>
+        <v>220164</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>Källslund, Sk</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447936</v>
+        <v>448037</v>
       </c>
       <c r="R98" t="n">
-        <v>6191255</v>
+        <v>6191156</v>
       </c>
       <c r="S98" t="n">
         <v>100</v>
@@ -11996,17 +12013,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1990-06-02</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1990-06-02</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Helianthemum nummularium/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12020,12 +12037,12 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>stig i tallskog</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>SkFlora    753270</t>
+          <t>SkFlora    144618</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12036,7 +12053,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
+          <t>Via Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12046,16 +12063,16 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202353</t>
+          <t>https://artportalen.se/Sighting/64198935</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>89719299</v>
+        <v>81370389</v>
       </c>
       <c r="B99" t="n">
-        <v>106244</v>
+        <v>106156</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12063,37 +12080,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221144</v>
+        <v>221141</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Källslund, 500 m OSO, Sk</t>
+          <t>SO Källslund, Sk</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447876</v>
+        <v>447837</v>
       </c>
       <c r="R99" t="n">
-        <v>6191194</v>
+        <v>6191153</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12117,12 +12134,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12133,6 +12150,11 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Gles tallskog</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -12142,22 +12164,26 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89719299</t>
+          <t>https://artportalen.se/Sighting/81370389</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>89719303</v>
+        <v>64202353</v>
       </c>
       <c r="B100" t="n">
-        <v>106244</v>
+        <v>106243</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12185,17 +12211,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Källslund, 400 m OSO, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447986</v>
+        <v>447936</v>
       </c>
       <c r="R100" t="n">
-        <v>6191225</v>
+        <v>6191255</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12219,12 +12245,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2003-07-01</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12235,6 +12266,16 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>stig i tallskog</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>SkFlora    753270</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12244,19 +12285,23 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89719303</t>
+          <t>https://artportalen.se/Sighting/64202353</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>93986216</v>
+        <v>89719299</v>
       </c>
       <c r="B101" t="n">
         <v>106244</v>
@@ -12287,14 +12332,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vittskövle driva. Prästlönebostället, 500 m NNV, Sk</t>
+          <t>Källslund, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>448061</v>
+        <v>447876</v>
       </c>
       <c r="R101" t="n">
-        <v>6191121</v>
+        <v>6191194</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12321,17 +12366,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>fint bestånd</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12357,13 +12397,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93986216</t>
+          <t>https://artportalen.se/Sighting/89719299</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>103450520</v>
+        <v>89719303</v>
       </c>
       <c r="B102" t="n">
         <v>106244</v>
@@ -12394,17 +12434,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 650 m NNV, Sk</t>
+          <t>Källslund, 400 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>448053</v>
+        <v>447986</v>
       </c>
       <c r="R102" t="n">
-        <v>6191276</v>
+        <v>6191225</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12428,17 +12468,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Tätt bestånd</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12449,11 +12484,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12463,19 +12493,19 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103450520</t>
+          <t>https://artportalen.se/Sighting/89719303</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117691151</v>
+        <v>93986216</v>
       </c>
       <c r="B103" t="n">
         <v>106244</v>
@@ -12506,14 +12536,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Källslund, 500 m OSO, Sk</t>
+          <t>Vittskövle driva. Prästlönebostället, 500 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447987</v>
+        <v>448061</v>
       </c>
       <c r="R103" t="n">
-        <v>6191212</v>
+        <v>6191121</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12540,12 +12570,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2021-05-29</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2021-05-29</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>fint bestånd</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12571,13 +12606,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117691151</t>
+          <t>https://artportalen.se/Sighting/93986216</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120870129</v>
+        <v>103450520</v>
       </c>
       <c r="B104" t="n">
         <v>106244</v>
@@ -12608,17 +12643,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Källslund, 750 m öster, Sk</t>
+          <t>Prästlönebostället, 650 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>448258</v>
+        <v>448053</v>
       </c>
       <c r="R104" t="n">
-        <v>6191267</v>
+        <v>6191276</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12642,12 +12677,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Tätt bestånd</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12661,7 +12701,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>Gles tallskog</t>
+          <t>gles tallskog</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12672,19 +12712,19 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Kjell-arne Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120870129</t>
+          <t>https://artportalen.se/Sighting/103450520</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120870156</v>
+        <v>117691151</v>
       </c>
       <c r="B105" t="n">
         <v>106244</v>
@@ -12715,14 +12755,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Källslund, 600 m OSO, Sk</t>
+          <t>Källslund, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>448200</v>
+        <v>447987</v>
       </c>
       <c r="R105" t="n">
-        <v>6191231</v>
+        <v>6191212</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12749,12 +12789,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12765,11 +12805,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>Gles tallskog</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12779,19 +12814,19 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120870156</t>
+          <t>https://artportalen.se/Sighting/117691151</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120870159</v>
+        <v>120870129</v>
       </c>
       <c r="B106" t="n">
         <v>106244</v>
@@ -12822,14 +12857,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Källslund, 600 m OSO, Sk</t>
+          <t>Källslund, 750 m öster, Sk</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>448143</v>
+        <v>448258</v>
       </c>
       <c r="R106" t="n">
-        <v>6191172</v>
+        <v>6191267</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12892,13 +12927,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120870159</t>
+          <t>https://artportalen.se/Sighting/120870129</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123704402</v>
+        <v>120870156</v>
       </c>
       <c r="B107" t="n">
         <v>106244</v>
@@ -12927,23 +12962,19 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Källslund, Sk</t>
+          <t>Källslund, 600 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>448139</v>
+        <v>448200</v>
       </c>
       <c r="R107" t="n">
-        <v>6191177</v>
+        <v>6191231</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12967,12 +12998,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12981,31 +13012,35 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Gles tallskog</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123704402</t>
+          <t>https://artportalen.se/Sighting/120870156</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126708481</v>
+        <v>120870159</v>
       </c>
       <c r="B108" t="n">
         <v>106244</v>
@@ -13034,27 +13069,19 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Tallskog på sand, Vittskövle driva, Sk</t>
+          <t>Källslund, 600 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>448062</v>
+        <v>448143</v>
       </c>
       <c r="R108" t="n">
-        <v>6191139</v>
+        <v>6191172</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13078,17 +13105,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Spridda bestånd. Visad under LBF-exkursion ledd av Kjöll-Arne Olsson.</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13097,79 +13119,80 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Gles tallskog</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Inger Arvidsson</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126708481</t>
+          <t>https://artportalen.se/Sighting/120870159</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>6834734</v>
+        <v>123704402</v>
       </c>
       <c r="B109" t="n">
-        <v>107517</v>
+        <v>106244</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221849</v>
+        <v>221144</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vittskövle driva, Sk</t>
+          <t>Källslund, Sk</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>448435</v>
+        <v>448139</v>
       </c>
       <c r="R109" t="n">
-        <v>6191261</v>
+        <v>6191177</v>
       </c>
       <c r="S109" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13193,12 +13216,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13207,73 +13230,77 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lars Erik Norbäck</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lars Erik Norbäck, Carl Jyker</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6834734</t>
+          <t>https://artportalen.se/Sighting/123704402</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>53941606</v>
+        <v>126708481</v>
       </c>
       <c r="B110" t="n">
-        <v>107517</v>
+        <v>106244</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221849</v>
+        <v>221144</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Vittskövle, Sk</t>
+          <t>Tallskog på sand, Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>448052</v>
+        <v>448062</v>
       </c>
       <c r="R110" t="n">
-        <v>6191252</v>
+        <v>6191139</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -13300,12 +13327,17 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2015-06-09</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2015-06-09</t>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Spridda bestånd. Visad under LBF-exkursion ledd av Kjöll-Arne Olsson.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13314,38 +13346,34 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Stefan Andersson, Inger Arvidsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/53941606</t>
+          <t>https://artportalen.se/Sighting/126708481</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>64199651</v>
+        <v>6834734</v>
       </c>
       <c r="B111" t="n">
-        <v>107516</v>
+        <v>107517</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13371,19 +13399,26 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>500m OSO Källslund, Sk</t>
+          <t>Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447937</v>
+        <v>448435</v>
       </c>
       <c r="R111" t="n">
-        <v>6191155</v>
+        <v>6191261</v>
       </c>
       <c r="S111" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13407,17 +13442,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
+          <t>2013-06-27</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Thymus serpyllum/2D8j3925/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>2013-06-27</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13428,45 +13458,31 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>skogsväg i gles tallskog</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>SkFlora    428606</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Lars Erik Norbäck</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Lars Erik Norbäck, Carl Jyker</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64199651</t>
+          <t>https://artportalen.se/Sighting/6834734</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>64200334</v>
+        <v>53941606</v>
       </c>
       <c r="B112" t="n">
-        <v>107516</v>
+        <v>107517</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13492,19 +13508,24 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>1,2 km V Ängagården, Sk</t>
+          <t>Vittskövle, Sk</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>448036</v>
+        <v>448052</v>
       </c>
       <c r="R112" t="n">
-        <v>6191256</v>
+        <v>6191252</v>
       </c>
       <c r="S112" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13528,17 +13549,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>2015-06-09</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Thymus serpyllum/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>2015-06-09</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13552,39 +13568,30 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>skogsväg, tallskog</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>SkFlora    511044</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Bengt Westman</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Bengt Westman</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64200334</t>
+          <t>https://artportalen.se/Sighting/53941606</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>64202342</v>
+        <v>64199651</v>
       </c>
       <c r="B113" t="n">
         <v>107516</v>
@@ -13615,14 +13622,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>500m OSO Källslund, Sk</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447936</v>
+        <v>447937</v>
       </c>
       <c r="R113" t="n">
-        <v>6191255</v>
+        <v>6191155</v>
       </c>
       <c r="S113" t="n">
         <v>100</v>
@@ -13649,17 +13656,17 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Thymus serpyllum/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Thymus serpyllum/2D8j3925/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13673,12 +13680,12 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>stig i tallskog</t>
+          <t>skogsväg i gles tallskog</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>SkFlora    753265</t>
+          <t>SkFlora    428606</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13699,16 +13706,16 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202342</t>
+          <t>https://artportalen.se/Sighting/64199651</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>78731946</v>
+        <v>64200334</v>
       </c>
       <c r="B114" t="n">
-        <v>107517</v>
+        <v>107516</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13733,29 +13740,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Källslund, 700 m öster, Sk</t>
+          <t>1,2 km V Ängagården, Sk</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>448266</v>
+        <v>448036</v>
       </c>
       <c r="R114" t="n">
-        <v>6191395</v>
+        <v>6191256</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13779,12 +13777,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13795,6 +13798,16 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>skogsväg, tallskog</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>SkFlora    511044</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13804,22 +13817,26 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78731946</t>
+          <t>https://artportalen.se/Sighting/64200334</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>78731949</v>
+        <v>64202342</v>
       </c>
       <c r="B115" t="n">
-        <v>107517</v>
+        <v>107516</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13844,29 +13861,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 480 m NNV, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>448065</v>
+        <v>447936</v>
       </c>
       <c r="R115" t="n">
-        <v>6191119</v>
+        <v>6191255</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13890,12 +13898,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2003-07-01</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13906,6 +13919,16 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>stig i tallskog</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>SkFlora    753265</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -13915,19 +13938,23 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78731949</t>
+          <t>https://artportalen.se/Sighting/64202342</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>81370263</v>
+        <v>78731946</v>
       </c>
       <c r="B116" t="n">
         <v>107517</v>
@@ -13955,20 +13982,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>SO Källslund, Sk</t>
+          <t>Källslund, 700 m öster, Sk</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447837</v>
+        <v>448266</v>
       </c>
       <c r="R116" t="n">
-        <v>6191153</v>
+        <v>6191395</v>
       </c>
       <c r="S116" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13992,12 +14028,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14008,11 +14044,6 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>Gles tallskog</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -14022,43 +14053,39 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t>Skånes Flora Millora 2008-2015</t>
-        </is>
-      </c>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81370263</t>
+          <t>https://artportalen.se/Sighting/78731946</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>64202388</v>
+        <v>78731949</v>
       </c>
       <c r="B117" t="n">
-        <v>97983</v>
+        <v>107517</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221945</v>
+        <v>221849</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -14066,20 +14093,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>Prästlönebostället, 480 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>448335</v>
+        <v>448065</v>
       </c>
       <c r="R117" t="n">
-        <v>6191260</v>
+        <v>6191119</v>
       </c>
       <c r="S117" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14103,17 +14139,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum/2D8j4029/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14124,16 +14155,6 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>SkFlora    753287</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -14143,26 +14164,22 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202388</t>
+          <t>https://artportalen.se/Sighting/78731949</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126708374</v>
+        <v>81370263</v>
       </c>
       <c r="B118" t="n">
-        <v>98050</v>
+        <v>107517</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14170,41 +14187,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>222112</v>
+        <v>221849</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Tallskog på sand, Vittskövle driva, Sk</t>
+          <t>SO Källslund, Sk</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>448062</v>
+        <v>447837</v>
       </c>
       <c r="R118" t="n">
-        <v>6191139</v>
+        <v>6191153</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14228,17 +14241,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Glest bestånd på stigen. Observerad under LBF-exkursion ledd av Kjell-Arne Olsson.</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14247,81 +14255,80 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Gles tallskog</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Inger Arvidsson</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126708374</t>
+          <t>https://artportalen.se/Sighting/81370263</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127333979</v>
+        <v>64202388</v>
       </c>
       <c r="B119" t="n">
-        <v>98050</v>
+        <v>97983</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222112</v>
+        <v>221945</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Vittskövle, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>448078</v>
+        <v>448335</v>
       </c>
       <c r="R119" t="n">
-        <v>6191244</v>
+        <v>6191260</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14345,12 +14352,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2003-07-01</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum/2D8j4029/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14364,7 +14376,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>sandig skogsväg</t>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>SkFlora    753287</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14378,53 +14395,65 @@
           <t>Kjell-arne Olsson</t>
         </is>
       </c>
-      <c r="AY119" t="inlineStr"/>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127333979</t>
+          <t>https://artportalen.se/Sighting/64202388</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>6282743</v>
+        <v>126708374</v>
       </c>
       <c r="B120" t="n">
-        <v>101348</v>
+        <v>98050</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>224913</v>
+        <v>222112</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Källslund, Sk</t>
+          <t>Tallskog på sand, Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>448037</v>
+        <v>448062</v>
       </c>
       <c r="R120" t="n">
-        <v>6191156</v>
+        <v>6191139</v>
       </c>
       <c r="S120" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14446,24 +14475,19 @@
           <t>Vittskövle</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Arkiv-M-Kri-0003</t>
-        </is>
-      </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>1990-04-05</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>1990-04-05</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>2D8j3926</t>
+          <t>Glest bestånd på stigen. Observerad under LBF-exkursion ledd av Kjell-Arne Olsson.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14472,31 +14496,256 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Inger Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126708374</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>127333979</v>
+      </c>
+      <c r="B121" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Vittskövle, Sk</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>448078</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6191244</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Vittskövle</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>sandig skogsväg</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127333979</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>6282743</v>
+      </c>
+      <c r="B122" t="n">
+        <v>101348</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Källslund, Sk</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>448037</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6191156</v>
+      </c>
+      <c r="S122" t="n">
+        <v>50</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Vittskövle</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Arkiv-M-Kri-0003</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>1990-04-05</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>1990-04-05</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>2D8j3926</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
           <t>Skåne Floraväktarna</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
+      <c r="AX122" t="inlineStr">
         <is>
           <t>Via Skåne Floraväktarna</t>
         </is>
       </c>
-      <c r="AY120" t="inlineStr">
+      <c r="AY122" t="inlineStr">
         <is>
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
+      <c r="AZ122" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6282743</t>
         </is>
@@ -14623,6 +14872,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106474</v>
+        <v>106476</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106474</v>
+        <v>106476</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ122"/>
+  <dimension ref="A1:AZ123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106476</v>
+        <v>106478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106476</v>
+        <v>106478</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11060,10 +11060,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89724948</v>
+        <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91329</v>
+        <v>91524</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11071,45 +11071,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4191</v>
+        <v>4188</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Källslund, 500 m OSO, Sk</t>
+          <t>Källslund, 600 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447876</v>
+        <v>448148</v>
       </c>
       <c r="R90" t="n">
-        <v>6191194</v>
+        <v>6191188</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11136,12 +11125,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11150,7 +11139,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11162,60 +11150,71 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Charlotte Wigermo, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89724948</t>
+          <t>https://artportalen.se/Sighting/137203946</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122450695</v>
+        <v>89724948</v>
       </c>
       <c r="B91" t="n">
-        <v>91930</v>
+        <v>91329</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5442</v>
+        <v>4191</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Källslund, 750 m OSO, Sk</t>
+          <t>Källslund, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>448292</v>
+        <v>447876</v>
       </c>
       <c r="R91" t="n">
-        <v>6191182</v>
+        <v>6191194</v>
       </c>
       <c r="S91" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11239,12 +11238,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11253,6 +11252,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11264,61 +11264,57 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Tony Svensson, Crister Albinsson, Carl-Axel Andersson, Patrik Celander, Ulf Gärdenfors</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Puggehatten, exkursion</t>
-        </is>
-      </c>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122450695</t>
+          <t>https://artportalen.se/Sighting/89724948</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117691153</v>
+        <v>122450695</v>
       </c>
       <c r="B92" t="n">
-        <v>58018</v>
+        <v>91930</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100094</v>
+        <v>5442</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sommargylling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Oriolus oriolus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Källslund, 500 m OSO, Sk</t>
+          <t>Källslund, 750 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447987</v>
+        <v>448292</v>
       </c>
       <c r="R92" t="n">
-        <v>6191212</v>
+        <v>6191182</v>
       </c>
       <c r="S92" t="n">
         <v>50</v>
@@ -11345,12 +11341,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11370,60 +11366,64 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Charlotte Wigermo, Tony Svensson, Crister Albinsson, Carl-Axel Andersson, Patrik Celander, Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117691153</t>
+          <t>https://artportalen.se/Sighting/122450695</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>80656754</v>
+        <v>117691153</v>
       </c>
       <c r="B93" t="n">
-        <v>45044</v>
+        <v>58018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102018</v>
+        <v>100094</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Sommargylling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Oriolus oriolus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 450 m NNV, Sk</t>
+          <t>Källslund, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447708</v>
+        <v>447987</v>
       </c>
       <c r="R93" t="n">
-        <v>6191230</v>
+        <v>6191212</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11447,12 +11447,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11478,54 +11478,54 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80656754</t>
+          <t>https://artportalen.se/Sighting/117691153</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>85929311</v>
+        <v>80656754</v>
       </c>
       <c r="B94" t="n">
-        <v>58238</v>
+        <v>45044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103012</v>
+        <v>102018</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 400 m NNO, Sk</t>
+          <t>Prästlönebostället, 450 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>448510</v>
+        <v>447708</v>
       </c>
       <c r="R94" t="n">
-        <v>6191039</v>
+        <v>6191230</v>
       </c>
       <c r="S94" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11549,12 +11549,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11580,16 +11580,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85929311</t>
+          <t>https://artportalen.se/Sighting/80656754</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122090041</v>
+        <v>85929311</v>
       </c>
       <c r="B95" t="n">
-        <v>56689</v>
+        <v>58238</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11597,45 +11597,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>206046</v>
+        <v>103012</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vittskövle driva, Sk</t>
+          <t>Prästlönebostället, 400 m NNO, Sk</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>448335</v>
+        <v>448510</v>
       </c>
       <c r="R95" t="n">
-        <v>6191260</v>
+        <v>6191039</v>
       </c>
       <c r="S95" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11659,22 +11651,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2020-05-31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2020-05-31</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11689,65 +11671,73 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Carl-Axel Andersson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122090041</t>
+          <t>https://artportalen.se/Sighting/85929311</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>64198940</v>
+        <v>122090041</v>
       </c>
       <c r="B96" t="n">
-        <v>99096</v>
+        <v>56689</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219798</v>
+        <v>206046</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Källslund, Sk</t>
+          <t>Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>448037</v>
+        <v>448335</v>
       </c>
       <c r="R96" t="n">
-        <v>6191156</v>
+        <v>6191260</v>
       </c>
       <c r="S96" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11771,17 +11761,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>1990-06-02</t>
+          <t>2025-01-11</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>1990-06-02</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Epipactis helleborine/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
+          <t>2025-01-11</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11792,80 +11787,66 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>SkFlora    144621</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Carl-Axel Andersson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Carl-Axel Andersson, Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64198940</t>
+          <t>https://artportalen.se/Sighting/122090041</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>64200341</v>
+        <v>64198940</v>
       </c>
       <c r="B97" t="n">
-        <v>108115</v>
+        <v>99096</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>1,2 km V Ängagården, Sk</t>
+          <t>Källslund, Sk</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>448036</v>
+        <v>448037</v>
       </c>
       <c r="R97" t="n">
-        <v>6191256</v>
+        <v>6191156</v>
       </c>
       <c r="S97" t="n">
         <v>100</v>
@@ -11892,17 +11873,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1990-06-02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1990-06-02</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Cirsium acaule/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Epipactis helleborine/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11916,12 +11897,12 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>skogsväg, tallskog</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>SkFlora    511048</t>
+          <t>SkFlora    144621</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11932,7 +11913,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
+          <t>Via Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11942,16 +11923,16 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64200341</t>
+          <t>https://artportalen.se/Sighting/64198940</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>64198935</v>
+        <v>64200341</v>
       </c>
       <c r="B98" t="n">
-        <v>104639</v>
+        <v>108115</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11959,34 +11940,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Källslund, Sk</t>
+          <t>1,2 km V Ängagården, Sk</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>448037</v>
+        <v>448036</v>
       </c>
       <c r="R98" t="n">
-        <v>6191156</v>
+        <v>6191256</v>
       </c>
       <c r="S98" t="n">
         <v>100</v>
@@ -12013,17 +11994,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>1990-06-02</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>1990-06-02</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
+          <t>Cirsium acaule/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12037,12 +12018,12 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>skogsväg, tallskog</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>SkFlora    144618</t>
+          <t>SkFlora    511048</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12053,7 +12034,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
+          <t>Kjell-arne Olsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12063,54 +12044,54 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64198935</t>
+          <t>https://artportalen.se/Sighting/64200341</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>81370389</v>
+        <v>64198935</v>
       </c>
       <c r="B99" t="n">
-        <v>106156</v>
+        <v>104639</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221141</v>
+        <v>220164</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>SO Källslund, Sk</t>
+          <t>Källslund, Sk</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447837</v>
+        <v>448037</v>
       </c>
       <c r="R99" t="n">
-        <v>6191153</v>
+        <v>6191156</v>
       </c>
       <c r="S99" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12134,12 +12115,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>1990-06-02</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>1990-06-02</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium/2D8j3926/Vittskövle s:n/LSv/ /Leif Svensson,Karlshamn</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12153,7 +12139,12 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Gles tallskog</t>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>SkFlora    144618</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -12164,26 +12155,26 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
+          <t>Via Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>Skånes Flora Millora 2008-2015</t>
+          <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81370389</t>
+          <t>https://artportalen.se/Sighting/64198935</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>64202353</v>
+        <v>81370389</v>
       </c>
       <c r="B100" t="n">
-        <v>106243</v>
+        <v>106156</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12191,37 +12182,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221144</v>
+        <v>221141</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>SO Källslund, Sk</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447936</v>
+        <v>447837</v>
       </c>
       <c r="R100" t="n">
-        <v>6191255</v>
+        <v>6191153</v>
       </c>
       <c r="S100" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12245,17 +12236,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12269,12 +12255,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>stig i tallskog</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>SkFlora    753270</t>
+          <t>Gles tallskog</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -12290,21 +12271,21 @@
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>Skånes Flora (1989-2006)</t>
+          <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202353</t>
+          <t>https://artportalen.se/Sighting/81370389</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>89719299</v>
+        <v>64202353</v>
       </c>
       <c r="B101" t="n">
-        <v>106244</v>
+        <v>106243</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12332,17 +12313,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Källslund, 500 m OSO, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447876</v>
+        <v>447936</v>
       </c>
       <c r="R101" t="n">
-        <v>6191194</v>
+        <v>6191255</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12366,12 +12347,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2003-07-01</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12382,6 +12368,16 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>stig i tallskog</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>SkFlora    753270</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12391,19 +12387,23 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89719299</t>
+          <t>https://artportalen.se/Sighting/64202353</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>89719303</v>
+        <v>89719299</v>
       </c>
       <c r="B102" t="n">
         <v>106244</v>
@@ -12434,14 +12434,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Källslund, 400 m OSO, Sk</t>
+          <t>Källslund, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447986</v>
+        <v>447876</v>
       </c>
       <c r="R102" t="n">
-        <v>6191225</v>
+        <v>6191194</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12499,13 +12499,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89719303</t>
+          <t>https://artportalen.se/Sighting/89719299</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>93986216</v>
+        <v>89719303</v>
       </c>
       <c r="B103" t="n">
         <v>106244</v>
@@ -12536,14 +12536,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Vittskövle driva. Prästlönebostället, 500 m NNV, Sk</t>
+          <t>Källslund, 400 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>448061</v>
+        <v>447986</v>
       </c>
       <c r="R103" t="n">
-        <v>6191121</v>
+        <v>6191225</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12570,17 +12570,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>fint bestånd</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12606,13 +12601,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93986216</t>
+          <t>https://artportalen.se/Sighting/89719303</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>103450520</v>
+        <v>93986216</v>
       </c>
       <c r="B104" t="n">
         <v>106244</v>
@@ -12643,17 +12638,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 650 m NNV, Sk</t>
+          <t>Vittskövle driva. Prästlönebostället, 500 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>448053</v>
+        <v>448061</v>
       </c>
       <c r="R104" t="n">
-        <v>6191276</v>
+        <v>6191121</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12677,17 +12672,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2021-05-29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2021-05-29</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Tätt bestånd</t>
+          <t>fint bestånd</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12698,11 +12693,6 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12712,19 +12702,19 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103450520</t>
+          <t>https://artportalen.se/Sighting/93986216</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>117691151</v>
+        <v>103450520</v>
       </c>
       <c r="B105" t="n">
         <v>106244</v>
@@ -12755,17 +12745,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Källslund, 500 m OSO, Sk</t>
+          <t>Prästlönebostället, 650 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447987</v>
+        <v>448053</v>
       </c>
       <c r="R105" t="n">
-        <v>6191212</v>
+        <v>6191276</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12789,12 +12779,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Tätt bestånd</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12805,6 +12800,11 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12814,19 +12814,19 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Kjell-arne Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117691151</t>
+          <t>https://artportalen.se/Sighting/103450520</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120870129</v>
+        <v>117691151</v>
       </c>
       <c r="B106" t="n">
         <v>106244</v>
@@ -12857,14 +12857,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Källslund, 750 m öster, Sk</t>
+          <t>Källslund, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>448258</v>
+        <v>447987</v>
       </c>
       <c r="R106" t="n">
-        <v>6191267</v>
+        <v>6191212</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12907,11 +12907,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Gles tallskog</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12921,19 +12916,19 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120870129</t>
+          <t>https://artportalen.se/Sighting/117691151</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120870156</v>
+        <v>120870129</v>
       </c>
       <c r="B107" t="n">
         <v>106244</v>
@@ -12964,14 +12959,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Källslund, 600 m OSO, Sk</t>
+          <t>Källslund, 750 m öster, Sk</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>448200</v>
+        <v>448258</v>
       </c>
       <c r="R107" t="n">
-        <v>6191231</v>
+        <v>6191267</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13034,13 +13029,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120870156</t>
+          <t>https://artportalen.se/Sighting/120870129</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120870159</v>
+        <v>120870156</v>
       </c>
       <c r="B108" t="n">
         <v>106244</v>
@@ -13075,10 +13070,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>448143</v>
+        <v>448200</v>
       </c>
       <c r="R108" t="n">
-        <v>6191172</v>
+        <v>6191231</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13141,13 +13136,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120870159</t>
+          <t>https://artportalen.se/Sighting/120870156</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123704402</v>
+        <v>120870159</v>
       </c>
       <c r="B109" t="n">
         <v>106244</v>
@@ -13176,23 +13171,19 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Källslund, Sk</t>
+          <t>Källslund, 600 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>448139</v>
+        <v>448143</v>
       </c>
       <c r="R109" t="n">
-        <v>6191177</v>
+        <v>6191172</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13216,12 +13207,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13230,31 +13221,35 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Gles tallskog</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123704402</t>
+          <t>https://artportalen.se/Sighting/120870159</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126708481</v>
+        <v>123704402</v>
       </c>
       <c r="B110" t="n">
         <v>106244</v>
@@ -13284,23 +13279,19 @@
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Tallskog på sand, Vittskövle driva, Sk</t>
+          <t>Källslund, Sk</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>448062</v>
+        <v>448139</v>
       </c>
       <c r="R110" t="n">
-        <v>6191139</v>
+        <v>6191177</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -13327,17 +13318,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Spridda bestånd. Visad under LBF-exkursion ledd av Kjöll-Arne Olsson.</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13353,72 +13339,73 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Inger Arvidsson</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126708481</t>
+          <t>https://artportalen.se/Sighting/123704402</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>6834734</v>
+        <v>126708481</v>
       </c>
       <c r="B111" t="n">
-        <v>107517</v>
+        <v>106244</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221849</v>
+        <v>221144</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Vittskövle driva, Sk</t>
+          <t>Tallskog på sand, Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>448435</v>
+        <v>448062</v>
       </c>
       <c r="R111" t="n">
-        <v>6191261</v>
+        <v>6191139</v>
       </c>
       <c r="S111" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13442,12 +13429,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Spridda bestånd. Visad under LBF-exkursion ledd av Kjöll-Arne Olsson.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13456,30 +13448,31 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lars Erik Norbäck</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Lars Erik Norbäck, Carl Jyker</t>
+          <t>Stefan Andersson, Inger Arvidsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6834734</t>
+          <t>https://artportalen.se/Sighting/126708481</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>53941606</v>
+        <v>6834734</v>
       </c>
       <c r="B112" t="n">
         <v>107517</v>
@@ -13508,24 +13501,26 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Vittskövle, Sk</t>
+          <t>Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>448052</v>
+        <v>448435</v>
       </c>
       <c r="R112" t="n">
-        <v>6191252</v>
+        <v>6191261</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13549,12 +13544,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2015-06-09</t>
+          <t>2013-06-27</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2015-06-09</t>
+          <t>2013-06-27</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13565,36 +13560,31 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Lars Erik Norbäck</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Lars Erik Norbäck, Carl Jyker</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/53941606</t>
+          <t>https://artportalen.se/Sighting/6834734</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>64199651</v>
+        <v>53941606</v>
       </c>
       <c r="B113" t="n">
-        <v>107516</v>
+        <v>107517</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13620,19 +13610,24 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>500m OSO Källslund, Sk</t>
+          <t>Vittskövle, Sk</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447937</v>
+        <v>448052</v>
       </c>
       <c r="R113" t="n">
-        <v>6191155</v>
+        <v>6191252</v>
       </c>
       <c r="S113" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13656,17 +13651,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
+          <t>2015-06-09</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>1998-06-12</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Thymus serpyllum/2D8j3925/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>2015-06-09</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13680,39 +13670,30 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>skogsväg i gles tallskog</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>SkFlora    428606</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Bengt Westman</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Bengt Westman</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64199651</t>
+          <t>https://artportalen.se/Sighting/53941606</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>64200334</v>
+        <v>64199651</v>
       </c>
       <c r="B114" t="n">
         <v>107516</v>
@@ -13743,14 +13724,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>1,2 km V Ängagården, Sk</t>
+          <t>500m OSO Källslund, Sk</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>448036</v>
+        <v>447937</v>
       </c>
       <c r="R114" t="n">
-        <v>6191256</v>
+        <v>6191155</v>
       </c>
       <c r="S114" t="n">
         <v>100</v>
@@ -13777,17 +13758,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1998-06-12</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Thymus serpyllum/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Thymus serpyllum/2D8j3925/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13801,12 +13782,12 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>skogsväg, tallskog</t>
+          <t>skogsväg i gles tallskog</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>SkFlora    511044</t>
+          <t>SkFlora    428606</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13827,13 +13808,13 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64200334</t>
+          <t>https://artportalen.se/Sighting/64199651</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>64202342</v>
+        <v>64200334</v>
       </c>
       <c r="B115" t="n">
         <v>107516</v>
@@ -13864,14 +13845,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>1,2 km V Ängagården, Sk</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447936</v>
+        <v>448036</v>
       </c>
       <c r="R115" t="n">
-        <v>6191255</v>
+        <v>6191256</v>
       </c>
       <c r="S115" t="n">
         <v>100</v>
@@ -13898,17 +13879,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Thymus serpyllum/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>Thymus serpyllum/2D8j4026/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13922,12 +13903,12 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>stig i tallskog</t>
+          <t>skogsväg, tallskog</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>SkFlora    753265</t>
+          <t>SkFlora    511044</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13948,16 +13929,16 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202342</t>
+          <t>https://artportalen.se/Sighting/64200334</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>78731946</v>
+        <v>64202342</v>
       </c>
       <c r="B116" t="n">
-        <v>107517</v>
+        <v>107516</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13982,29 +13963,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Källslund, 700 m öster, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>448266</v>
+        <v>447936</v>
       </c>
       <c r="R116" t="n">
-        <v>6191395</v>
+        <v>6191255</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14028,12 +14000,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2003-07-01</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum/2D8j4025/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14044,6 +14021,16 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>stig i tallskog</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>SkFlora    753265</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -14053,19 +14040,23 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78731946</t>
+          <t>https://artportalen.se/Sighting/64202342</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>78731949</v>
+        <v>78731946</v>
       </c>
       <c r="B117" t="n">
         <v>107517</v>
@@ -14095,7 +14086,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14105,14 +14096,14 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Prästlönebostället, 480 m NNV, Sk</t>
+          <t>Källslund, 700 m öster, Sk</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>448065</v>
+        <v>448266</v>
       </c>
       <c r="R117" t="n">
-        <v>6191119</v>
+        <v>6191395</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14170,13 +14161,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78731949</t>
+          <t>https://artportalen.se/Sighting/78731946</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>81370263</v>
+        <v>78731949</v>
       </c>
       <c r="B118" t="n">
         <v>107517</v>
@@ -14204,20 +14195,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>SO Källslund, Sk</t>
+          <t>Prästlönebostället, 480 m NNV, Sk</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447837</v>
+        <v>448065</v>
       </c>
       <c r="R118" t="n">
-        <v>6191153</v>
+        <v>6191119</v>
       </c>
       <c r="S118" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14241,12 +14241,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14257,11 +14257,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>Gles tallskog</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -14271,43 +14266,39 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t>Skånes Flora Millora 2008-2015</t>
-        </is>
-      </c>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81370263</t>
+          <t>https://artportalen.se/Sighting/78731949</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>64202388</v>
+        <v>81370263</v>
       </c>
       <c r="B119" t="n">
-        <v>97983</v>
+        <v>107517</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221945</v>
+        <v>221849</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -14318,17 +14309,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>mln Källslund och Drivan, Sk</t>
+          <t>SO Källslund, Sk</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>448335</v>
+        <v>447837</v>
       </c>
       <c r="R119" t="n">
-        <v>6191260</v>
+        <v>6191153</v>
       </c>
       <c r="S119" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14352,17 +14343,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum/2D8j4029/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14376,12 +14362,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>SkFlora    753287</t>
+          <t>Gles tallskog</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14397,63 +14378,59 @@
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>Skånes Flora (1989-2006)</t>
+          <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64202388</t>
+          <t>https://artportalen.se/Sighting/81370263</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126708374</v>
+        <v>64202388</v>
       </c>
       <c r="B120" t="n">
-        <v>98050</v>
+        <v>97983</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>222112</v>
+        <v>221945</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Tallskog på sand, Vittskövle driva, Sk</t>
+          <t>mln Källslund och Drivan, Sk</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>448062</v>
+        <v>448335</v>
       </c>
       <c r="R120" t="n">
-        <v>6191139</v>
+        <v>6191260</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14477,17 +14454,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Glest bestånd på stigen. Observerad under LBF-exkursion ledd av Kjell-Arne Olsson.</t>
+          <t>Lycopodium annotinum/2D8j4029/Vittskövle s:n/KAO/ /Kjell-Arne Olsson,Kristianstad</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14496,31 +14473,44 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>SkFlora    753287</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Inger Arvidsson</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126708374</t>
+          <t>https://artportalen.se/Sighting/64202388</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127333979</v>
+        <v>126708374</v>
       </c>
       <c r="B121" t="n">
         <v>98050</v>
@@ -14548,29 +14538,24 @@
           <t>(L.) Sw.</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Vittskövle, Sk</t>
+          <t>Tallskog på sand, Vittskövle driva, Sk</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>448078</v>
+        <v>448062</v>
       </c>
       <c r="R121" t="n">
-        <v>6191244</v>
+        <v>6191139</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14602,78 +14587,92 @@
           <t>2025-07-16</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Glest bestånd på stigen. Observerad under LBF-exkursion ledd av Kjell-Arne Olsson.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>sandig skogsväg</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
+          <t>Stefan Andersson, Inger Arvidsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127333979</t>
+          <t>https://artportalen.se/Sighting/126708374</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>6282743</v>
+        <v>127333979</v>
       </c>
       <c r="B122" t="n">
-        <v>101348</v>
+        <v>98050</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>224913</v>
+        <v>222112</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Källslund, Sk</t>
+          <t>Vittskövle, Sk</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>448037</v>
+        <v>448078</v>
       </c>
       <c r="R122" t="n">
-        <v>6191156</v>
+        <v>6191244</v>
       </c>
       <c r="S122" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14695,24 +14694,14 @@
           <t>Vittskövle</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Arkiv-M-Kri-0003</t>
-        </is>
-      </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>1990-04-05</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>1990-04-05</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>2D8j3926</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14726,26 +14715,139 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>sandig skogsväg</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127333979</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>6282743</v>
+      </c>
+      <c r="B123" t="n">
+        <v>101348</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Källslund, Sk</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>448037</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6191156</v>
+      </c>
+      <c r="S123" t="n">
+        <v>50</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Vittskövle</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Arkiv-M-Kri-0003</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>1990-04-05</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>1990-04-05</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>2D8j3926</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
           <t>Skåne Floraväktarna</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
+      <c r="AX123" t="inlineStr">
         <is>
           <t>Via Skåne Floraväktarna</t>
         </is>
       </c>
-      <c r="AY122" t="inlineStr">
+      <c r="AY123" t="inlineStr">
         <is>
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
+      <c r="AZ123" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6282743</t>
         </is>
@@ -14874,6 +14976,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106478</v>
+        <v>106491</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106478</v>
+        <v>106491</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91524</v>
+        <v>91537</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Gunnar Janson</t>
+          <t>Gunnar Janson, Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106491</v>
+        <v>106493</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106491</v>
+        <v>106493</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91537</v>
+        <v>91539</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106493</v>
+        <v>106497</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106493</v>
+        <v>106497</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91539</v>
+        <v>91542</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Gunnar Janson, Charlotte Wigermo</t>
+          <t>Charlotte Wigermo, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106497</v>
+        <v>106516</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106497</v>
+        <v>106516</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106516</v>
+        <v>106517</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106516</v>
+        <v>106517</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Gunnar Janson</t>
+          <t>Gunnar Janson, Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106517</v>
+        <v>106522</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106517</v>
+        <v>106522</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106522</v>
+        <v>106525</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106522</v>
+        <v>106525</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Gunnar Janson, Charlotte Wigermo</t>
+          <t>Charlotte Wigermo, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106525</v>
+        <v>106531</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106525</v>
+        <v>106531</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Gunnar Janson</t>
+          <t>Gunnar Janson, Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106531</v>
+        <v>106532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106531</v>
+        <v>106532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Gunnar Janson, Charlotte Wigermo</t>
+          <t>Charlotte Wigermo, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106532</v>
+        <v>106544</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106532</v>
+        <v>106544</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Gunnar Janson</t>
+          <t>Gunnar Janson, Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106544</v>
+        <v>106545</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106544</v>
+        <v>106545</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106545</v>
+        <v>106548</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106545</v>
+        <v>106548</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Gunnar Janson, Charlotte Wigermo</t>
+          <t>Charlotte Wigermo, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106548</v>
+        <v>106554</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106548</v>
+        <v>106554</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>137203946</v>
       </c>
       <c r="B90" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Gunnar Janson</t>
+          <t>Gunnar Janson, Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6129,7 +6129,7 @@
         <v>137154797</v>
       </c>
       <c r="B48" t="n">
-        <v>106554</v>
+        <v>106556</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>137162114</v>
       </c>
       <c r="B49" t="n">
-        <v>106554</v>
+        <v>106556</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Gunnar Janson</t>
+          <t>Gunnar Janson, Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">

--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -6359,7 +6359,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Gunnar Janson, Charlotte Wigermo</t>
+          <t>Charlotte Wigermo, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Gunnar Janson, Charlotte Wigermo</t>
+          <t>Charlotte Wigermo, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
